--- a/artfynd/A 39528-2021 artfynd.xlsx
+++ b/artfynd/A 39528-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39528-2021 artfynd.xlsx
+++ b/artfynd/A 39528-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -918,234 +918,6 @@
           <t>Ecogain</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>113169966</v>
-      </c>
-      <c r="B4" t="n">
-        <v>79587</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>562505</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6896674</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På äldre Asp</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>113168507</v>
-      </c>
-      <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>562320</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6896738</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39528-2021 artfynd.xlsx
+++ b/artfynd/A 39528-2021 artfynd.xlsx
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105545526</v>
+        <v>105545607</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>562319.5553322588</v>
+        <v>562505</v>
       </c>
       <c r="R2" t="n">
-        <v>6896737.840270511</v>
+        <v>6896674</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +743,14 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På äldre asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,50 +781,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105545607</v>
+        <v>105545526</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>562505.437288772</v>
+        <v>562320</v>
       </c>
       <c r="R3" t="n">
-        <v>6896673.583660003</v>
+        <v>6896738</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +858,9 @@
           <t>2022-08-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På äldre asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
